--- a/calc_data.xlsx
+++ b/calc_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ElliottCurtis-Young\Desktop\Coding Stuff\solar calculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4D4B4DC-743C-4BE7-AE70-632E6FD2554C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7053B6A6-6B95-4232-8592-AD29C7202E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D8994423-8BC9-4B61-AC29-906070D7403E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D8994423-8BC9-4B61-AC29-906070D7403E}"/>
   </bookViews>
   <sheets>
     <sheet name="calc_data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Generator output</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>Battery rate</t>
-  </si>
-  <si>
-    <t>Generator runtime</t>
   </si>
 </sst>
 </file>
@@ -196,7 +193,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -402,12 +399,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -433,24 +424,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -654,7 +627,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -663,10 +636,7 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -675,34 +645,28 @@
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="44" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="45" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1080,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC3E1373-D6FE-417F-87ED-789AD5A17FB9}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G237"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -1111,18 +1075,15 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="13">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="17">
-        <v>6</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>1</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>2</v>
       </c>
       <c r="D2" s="2">
@@ -1136,47 +1097,43 @@
         <f>IF(C2=0, 0, IF(C2&gt;3, 14.4, IF(C2=2, 8.6, 12.9)))</f>
         <v>8.6</v>
       </c>
-      <c r="G2" s="1">
-        <v>1731.0166670000001</v>
-      </c>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="13">
         <v>6</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>1</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>1.8</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E34" si="0">C3*4.8</f>
+        <f t="shared" ref="E3:E7" si="0">C3*4.8</f>
         <v>9.6</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F34" si="1">IF(C3=0, 0, IF(C3&gt;3, 14.4, IF(C3=2, 8.6, 12.9)))</f>
+        <f t="shared" ref="F3:F7" si="1">IF(C3=0, 0, IF(C3&gt;3, 14.4, IF(C3=2, 8.6, 12.9)))</f>
         <v>8.6</v>
       </c>
-      <c r="G3" s="1">
-        <v>1343.05</v>
-      </c>
+      <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="17">
+      <c r="A4" s="13">
         <v>6</v>
       </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="D4" s="4">
-        <v>1.8</v>
+      <c r="C4" s="6">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
@@ -1186,22 +1143,20 @@
         <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
-      <c r="G4" s="1">
-        <v>1343.05</v>
-      </c>
+      <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17">
+      <c r="A5" s="13">
         <v>6</v>
       </c>
-      <c r="B5" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="C5" s="7">
+      <c r="B5" s="5">
         <v>2</v>
       </c>
-      <c r="D5" s="2">
-        <v>0</v>
+      <c r="C5" s="6">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1.8</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
@@ -1211,22 +1166,20 @@
         <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
-      <c r="G5" s="1">
-        <v>4231.7333330000001</v>
-      </c>
+      <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17">
+      <c r="A6" s="13">
         <v>6</v>
       </c>
-      <c r="B6" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="C6" s="7">
+      <c r="B6" s="7">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6">
         <v>2</v>
       </c>
-      <c r="D6" s="3">
-        <v>1.8</v>
+      <c r="D6" s="2">
+        <v>0</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
@@ -1236,21 +1189,19 @@
         <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
-      <c r="G6" s="1">
-        <v>3858.7</v>
-      </c>
+      <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="17">
+      <c r="A7" s="13">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="B7" s="7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="6">
         <v>2</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>1.8</v>
       </c>
       <c r="E7">
@@ -1261,683 +1212,5076 @@
         <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
-      <c r="G7" s="1">
-        <v>3858.7</v>
-      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="17">
+      <c r="A8" s="13">
         <v>6</v>
       </c>
-      <c r="B8" s="8">
-        <v>5</v>
-      </c>
-      <c r="C8" s="7">
+      <c r="B8" s="5">
+        <v>4</v>
+      </c>
+      <c r="C8" s="6">
         <v>2</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
+        <f>C8*4.8</f>
         <v>9.6</v>
       </c>
       <c r="F8">
-        <f t="shared" si="1"/>
+        <f>IF(C8=0, 0, IF(C8&gt;3, 14.4, IF(C8=2, 8.6, 12.9)))</f>
         <v>8.6</v>
       </c>
-      <c r="G8" s="1">
-        <v>8156.8666670000002</v>
-      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="17">
+      <c r="A9" s="13">
         <v>6</v>
       </c>
-      <c r="B9" s="8">
-        <v>5</v>
-      </c>
-      <c r="C9" s="7">
+      <c r="B9" s="5">
+        <v>4</v>
+      </c>
+      <c r="C9" s="6">
         <v>2</v>
       </c>
       <c r="D9" s="3">
         <v>1.8</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E9:E21" si="2">C9*4.8</f>
         <v>9.6</v>
       </c>
       <c r="F9">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F9:F21" si="3">IF(C9=0, 0, IF(C9&gt;3, 14.4, IF(C9=2, 8.6, 12.9)))</f>
         <v>8.6</v>
       </c>
-      <c r="G9">
-        <v>7811.2</v>
-      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="17">
+      <c r="A10" s="13">
         <v>6</v>
       </c>
-      <c r="B10" s="8">
-        <v>5</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="B10" s="5">
+        <v>5</v>
+      </c>
+      <c r="C10" s="6">
         <v>2</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="2"/>
+        <v>9.6</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="3"/>
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="13">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3">
         <v>1.8</v>
       </c>
-      <c r="E10">
-        <f t="shared" si="0"/>
+      <c r="E11">
+        <f t="shared" si="2"/>
         <v>9.6</v>
       </c>
-      <c r="F10">
-        <f t="shared" si="1"/>
+      <c r="F11">
+        <f t="shared" si="3"/>
         <v>8.6</v>
       </c>
-      <c r="G10" s="1">
-        <v>7811.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
-        <v>20</v>
-      </c>
-      <c r="B11" s="10">
-        <v>5</v>
-      </c>
-      <c r="C11" s="11">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="1"/>
-        <v>12.9</v>
-      </c>
-      <c r="G11" s="1">
-        <v>2669.4</v>
-      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
-        <v>20</v>
-      </c>
-      <c r="B12" s="10">
-        <v>5</v>
-      </c>
-      <c r="C12" s="11">
-        <v>3</v>
-      </c>
-      <c r="D12" s="5">
-        <v>4.45</v>
+      <c r="A12" s="13">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
       </c>
       <c r="E12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>14.399999999999999</v>
       </c>
       <c r="F12">
-        <f t="shared" si="1"/>
-        <v>12.9</v>
-      </c>
-      <c r="G12" s="1">
-        <v>2428.6833329999999</v>
+        <f t="shared" si="3"/>
+        <v>12.9</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
-        <v>20</v>
-      </c>
-      <c r="B13" s="10">
-        <v>5</v>
-      </c>
-      <c r="C13" s="11">
-        <v>4</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
+      <c r="A13" s="13">
+        <v>6</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6">
+        <v>3</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.8</v>
       </c>
       <c r="E13">
-        <f t="shared" si="0"/>
-        <v>19.2</v>
+        <f t="shared" si="2"/>
+        <v>14.399999999999999</v>
       </c>
       <c r="F13">
-        <f t="shared" si="1"/>
-        <v>14.4</v>
-      </c>
-      <c r="G13" s="1">
-        <v>2668.8666669999998</v>
+        <f t="shared" si="3"/>
+        <v>12.9</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
-        <v>20</v>
-      </c>
-      <c r="B14" s="10">
-        <v>5</v>
-      </c>
-      <c r="C14" s="11">
-        <v>4</v>
-      </c>
-      <c r="D14" s="5">
-        <v>4.45</v>
+      <c r="A14" s="13">
+        <v>6</v>
+      </c>
+      <c r="B14" s="5">
+        <v>2</v>
+      </c>
+      <c r="C14" s="6">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
-        <v>19.2</v>
+        <f t="shared" si="2"/>
+        <v>14.399999999999999</v>
       </c>
       <c r="F14">
-        <f t="shared" si="1"/>
-        <v>14.4</v>
-      </c>
-      <c r="G14" s="1">
-        <v>2428</v>
+        <f t="shared" si="3"/>
+        <v>12.9</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
-        <v>20</v>
-      </c>
-      <c r="B15" s="12">
+      <c r="A15" s="13">
+        <v>6</v>
+      </c>
+      <c r="B15" s="5">
+        <v>2</v>
+      </c>
+      <c r="C15" s="6">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="3"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="13">
+        <v>6</v>
+      </c>
+      <c r="B16" s="7">
+        <v>3</v>
+      </c>
+      <c r="C16" s="6">
+        <v>3</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="2"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="3"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="13">
+        <v>6</v>
+      </c>
+      <c r="B17" s="7">
+        <v>3</v>
+      </c>
+      <c r="C17" s="6">
+        <v>3</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="3"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="13">
+        <v>6</v>
+      </c>
+      <c r="B18" s="5">
+        <v>4</v>
+      </c>
+      <c r="C18" s="6">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="2"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="3"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
+        <v>6</v>
+      </c>
+      <c r="B19" s="5">
+        <v>4</v>
+      </c>
+      <c r="C19" s="6">
+        <v>3</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="3"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="13">
+        <v>6</v>
+      </c>
+      <c r="B20" s="5">
+        <v>5</v>
+      </c>
+      <c r="C20" s="6">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="2"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="3"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="13">
+        <v>6</v>
+      </c>
+      <c r="B21" s="5">
+        <v>5</v>
+      </c>
+      <c r="C21" s="6">
+        <v>3</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="3"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>20</v>
+      </c>
+      <c r="B22" s="9">
+        <v>1</v>
+      </c>
+      <c r="C22" s="10">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <f>C22*4.8</f>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F22">
+        <f>IF(C22=0, 0, IF(C22&gt;3, 14.4, IF(C22=2, 8.6, 12.9)))</f>
+        <v>12.9</v>
+      </c>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
+        <v>20</v>
+      </c>
+      <c r="B23" s="9">
+        <v>1</v>
+      </c>
+      <c r="C23" s="10">
+        <v>3</v>
+      </c>
+      <c r="D23" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E23">
+        <f>C23*4.8</f>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F23">
+        <f>IF(C23=0, 0, IF(C23&gt;3, 14.4, IF(C23=2, 8.6, 12.9)))</f>
+        <v>12.9</v>
+      </c>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
+        <v>20</v>
+      </c>
+      <c r="B24" s="9">
+        <v>1</v>
+      </c>
+      <c r="C24" s="10">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E24">
+        <f>C24*4.8</f>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F24">
+        <f>IF(C24=0, 0, IF(C24&gt;3, 14.4, IF(C24=2, 8.6, 12.9)))</f>
+        <v>12.9</v>
+      </c>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
+        <v>20</v>
+      </c>
+      <c r="B25" s="9">
+        <v>1</v>
+      </c>
+      <c r="C25" s="10">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <f>C25*4.8</f>
+        <v>19.2</v>
+      </c>
+      <c r="F25">
+        <f>IF(C25=0, 0, IF(C25&gt;3, 14.4, IF(C25=2, 8.6, 12.9)))</f>
+        <v>14.4</v>
+      </c>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
+        <v>20</v>
+      </c>
+      <c r="B26" s="11">
+        <v>1</v>
+      </c>
+      <c r="C26" s="10">
+        <v>4</v>
+      </c>
+      <c r="D26" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E26">
+        <f>C26*4.8</f>
+        <v>19.2</v>
+      </c>
+      <c r="F26">
+        <f>IF(C26=0, 0, IF(C26&gt;3, 14.4, IF(C26=2, 8.6, 12.9)))</f>
+        <v>14.4</v>
+      </c>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <v>20</v>
+      </c>
+      <c r="B27" s="11">
+        <v>1</v>
+      </c>
+      <c r="C27" s="10">
+        <v>4</v>
+      </c>
+      <c r="D27" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E27">
+        <f>C27*4.8</f>
+        <v>19.2</v>
+      </c>
+      <c r="F27">
+        <f>IF(C27=0, 0, IF(C27&gt;3, 14.4, IF(C27=2, 8.6, 12.9)))</f>
+        <v>14.4</v>
+      </c>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <v>20</v>
+      </c>
+      <c r="B28" s="11">
+        <v>1</v>
+      </c>
+      <c r="C28" s="10">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <f>C28*4.8</f>
+        <v>24</v>
+      </c>
+      <c r="F28">
+        <f>IF(C28=0, 0, IF(C28&gt;3, 14.4, IF(C28=2, 8.6, 12.9)))</f>
+        <v>14.4</v>
+      </c>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>20</v>
+      </c>
+      <c r="B29" s="11">
+        <v>1</v>
+      </c>
+      <c r="C29" s="10">
+        <v>5</v>
+      </c>
+      <c r="D29" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E29">
+        <f>C29*4.8</f>
+        <v>24</v>
+      </c>
+      <c r="F29">
+        <f>IF(C29=0, 0, IF(C29&gt;3, 14.4, IF(C29=2, 8.6, 12.9)))</f>
+        <v>14.4</v>
+      </c>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <v>20</v>
+      </c>
+      <c r="B30" s="12">
+        <v>1</v>
+      </c>
+      <c r="C30" s="10">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E30">
+        <f>C30*4.8</f>
+        <v>24</v>
+      </c>
+      <c r="F30">
+        <f>IF(C30=0, 0, IF(C30&gt;3, 14.4, IF(C30=2, 8.6, 12.9)))</f>
+        <v>14.4</v>
+      </c>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>20</v>
+      </c>
+      <c r="B31" s="9">
+        <v>2</v>
+      </c>
+      <c r="C31" s="10">
+        <v>3</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <f>C31*4.8</f>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F31">
+        <f>IF(C31=0, 0, IF(C31&gt;3, 14.4, IF(C31=2, 8.6, 12.9)))</f>
+        <v>12.9</v>
+      </c>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>20</v>
+      </c>
+      <c r="B32" s="9">
+        <v>2</v>
+      </c>
+      <c r="C32" s="10">
+        <v>3</v>
+      </c>
+      <c r="D32" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E32">
+        <f>C32*4.8</f>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F32">
+        <f>IF(C32=0, 0, IF(C32&gt;3, 14.4, IF(C32=2, 8.6, 12.9)))</f>
+        <v>12.9</v>
+      </c>
+      <c r="G32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>20</v>
+      </c>
+      <c r="B33" s="9">
+        <v>2</v>
+      </c>
+      <c r="C33" s="10">
+        <v>3</v>
+      </c>
+      <c r="D33" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E33">
+        <f>C33*4.8</f>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F33">
+        <f>IF(C33=0, 0, IF(C33&gt;3, 14.4, IF(C33=2, 8.6, 12.9)))</f>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>20</v>
+      </c>
+      <c r="B34" s="9">
+        <v>2</v>
+      </c>
+      <c r="C34" s="10">
+        <v>4</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <f t="shared" ref="E34:E97" si="4">C34*4.8</f>
+        <v>19.2</v>
+      </c>
+      <c r="F34">
+        <f t="shared" ref="F34:F97" si="5">IF(C34=0, 0, IF(C34&gt;3, 14.4, IF(C34=2, 8.6, 12.9)))</f>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <v>20</v>
+      </c>
+      <c r="B35" s="9">
+        <v>2</v>
+      </c>
+      <c r="C35" s="10">
+        <v>4</v>
+      </c>
+      <c r="D35" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <v>20</v>
+      </c>
+      <c r="B36" s="9">
+        <v>2</v>
+      </c>
+      <c r="C36" s="10">
+        <v>4</v>
+      </c>
+      <c r="D36" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
+        <v>20</v>
+      </c>
+      <c r="B37" s="9">
+        <v>2</v>
+      </c>
+      <c r="C37" s="10">
+        <v>5</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="8">
+        <v>20</v>
+      </c>
+      <c r="B38" s="9">
+        <v>2</v>
+      </c>
+      <c r="C38" s="10">
+        <v>5</v>
+      </c>
+      <c r="D38" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="8">
+        <v>20</v>
+      </c>
+      <c r="B39" s="9">
+        <v>2</v>
+      </c>
+      <c r="C39" s="10">
+        <v>5</v>
+      </c>
+      <c r="D39" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="8">
+        <v>20</v>
+      </c>
+      <c r="B40" s="9">
+        <v>3</v>
+      </c>
+      <c r="C40" s="10">
+        <v>3</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="8">
+        <v>20</v>
+      </c>
+      <c r="B41" s="9">
+        <v>3</v>
+      </c>
+      <c r="C41" s="10">
+        <v>3</v>
+      </c>
+      <c r="D41" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="8">
+        <v>20</v>
+      </c>
+      <c r="B42" s="9">
+        <v>3</v>
+      </c>
+      <c r="C42" s="10">
+        <v>3</v>
+      </c>
+      <c r="D42" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="8">
+        <v>20</v>
+      </c>
+      <c r="B43" s="9">
+        <v>3</v>
+      </c>
+      <c r="C43" s="10">
+        <v>4</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="8">
+        <v>20</v>
+      </c>
+      <c r="B44" s="9">
+        <v>3</v>
+      </c>
+      <c r="C44" s="10">
+        <v>4</v>
+      </c>
+      <c r="D44" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="8">
+        <v>20</v>
+      </c>
+      <c r="B45" s="9">
+        <v>3</v>
+      </c>
+      <c r="C45" s="10">
+        <v>4</v>
+      </c>
+      <c r="D45" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="8">
+        <v>20</v>
+      </c>
+      <c r="B46" s="9">
+        <v>3</v>
+      </c>
+      <c r="C46" s="10">
+        <v>5</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="8">
+        <v>20</v>
+      </c>
+      <c r="B47" s="9">
+        <v>3</v>
+      </c>
+      <c r="C47" s="10">
+        <v>5</v>
+      </c>
+      <c r="D47" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="8">
+        <v>20</v>
+      </c>
+      <c r="B48" s="9">
+        <v>3</v>
+      </c>
+      <c r="C48" s="10">
+        <v>5</v>
+      </c>
+      <c r="D48" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="8">
+        <v>20</v>
+      </c>
+      <c r="B49" s="14">
+        <v>4</v>
+      </c>
+      <c r="C49" s="10">
+        <v>3</v>
+      </c>
+      <c r="D49" s="2">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="8">
+        <v>20</v>
+      </c>
+      <c r="B50" s="14">
+        <v>4</v>
+      </c>
+      <c r="C50" s="10">
+        <v>3</v>
+      </c>
+      <c r="D50" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="8">
+        <v>20</v>
+      </c>
+      <c r="B51" s="14">
+        <v>4</v>
+      </c>
+      <c r="C51" s="10">
+        <v>3</v>
+      </c>
+      <c r="D51" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="8">
+        <v>20</v>
+      </c>
+      <c r="B52" s="14">
+        <v>4</v>
+      </c>
+      <c r="C52" s="10">
+        <v>4</v>
+      </c>
+      <c r="D52" s="2">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="8">
+        <v>20</v>
+      </c>
+      <c r="B53" s="14">
+        <v>4</v>
+      </c>
+      <c r="C53" s="10">
+        <v>4</v>
+      </c>
+      <c r="D53" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="8">
+        <v>20</v>
+      </c>
+      <c r="B54" s="14">
+        <v>4</v>
+      </c>
+      <c r="C54" s="10">
+        <v>4</v>
+      </c>
+      <c r="D54" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="8">
+        <v>20</v>
+      </c>
+      <c r="B55" s="14">
+        <v>4</v>
+      </c>
+      <c r="C55" s="10">
+        <v>5</v>
+      </c>
+      <c r="D55" s="2">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="8">
+        <v>20</v>
+      </c>
+      <c r="B56" s="14">
+        <v>4</v>
+      </c>
+      <c r="C56" s="10">
+        <v>5</v>
+      </c>
+      <c r="D56" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="8">
+        <v>20</v>
+      </c>
+      <c r="B57" s="14">
+        <v>4</v>
+      </c>
+      <c r="C57" s="10">
+        <v>5</v>
+      </c>
+      <c r="D57" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="8">
+        <v>20</v>
+      </c>
+      <c r="B58" s="14">
+        <v>5</v>
+      </c>
+      <c r="C58" s="10">
+        <v>3</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="8">
+        <v>20</v>
+      </c>
+      <c r="B59" s="14">
+        <v>5</v>
+      </c>
+      <c r="C59" s="10">
+        <v>3</v>
+      </c>
+      <c r="D59" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="8">
+        <v>20</v>
+      </c>
+      <c r="B60" s="14">
+        <v>5</v>
+      </c>
+      <c r="C60" s="10">
+        <v>3</v>
+      </c>
+      <c r="D60" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="8">
+        <v>20</v>
+      </c>
+      <c r="B61" s="14">
+        <v>5</v>
+      </c>
+      <c r="C61" s="10">
+        <v>4</v>
+      </c>
+      <c r="D61" s="2">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="8">
+        <v>20</v>
+      </c>
+      <c r="B62" s="14">
+        <v>5</v>
+      </c>
+      <c r="C62" s="10">
+        <v>4</v>
+      </c>
+      <c r="D62" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="8">
+        <v>20</v>
+      </c>
+      <c r="B63" s="14">
+        <v>5</v>
+      </c>
+      <c r="C63" s="10">
+        <v>4</v>
+      </c>
+      <c r="D63" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="8">
+        <v>20</v>
+      </c>
+      <c r="B64" s="14">
+        <v>5</v>
+      </c>
+      <c r="C64" s="10">
+        <v>5</v>
+      </c>
+      <c r="D64" s="2">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="8">
+        <v>20</v>
+      </c>
+      <c r="B65" s="14">
+        <v>5</v>
+      </c>
+      <c r="C65" s="10">
+        <v>5</v>
+      </c>
+      <c r="D65" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="8">
+        <v>20</v>
+      </c>
+      <c r="B66" s="14">
+        <v>5</v>
+      </c>
+      <c r="C66" s="10">
+        <v>5</v>
+      </c>
+      <c r="D66" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="8">
+        <v>20</v>
+      </c>
+      <c r="B67" s="14">
+        <v>6</v>
+      </c>
+      <c r="C67" s="10">
+        <v>3</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="8">
+        <v>20</v>
+      </c>
+      <c r="B68" s="14">
+        <v>6</v>
+      </c>
+      <c r="C68" s="10">
+        <v>3</v>
+      </c>
+      <c r="D68" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="8">
+        <v>20</v>
+      </c>
+      <c r="B69" s="14">
+        <v>6</v>
+      </c>
+      <c r="C69" s="10">
+        <v>3</v>
+      </c>
+      <c r="D69" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="8">
+        <v>20</v>
+      </c>
+      <c r="B70" s="14">
+        <v>6</v>
+      </c>
+      <c r="C70" s="10">
+        <v>4</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="8">
+        <v>20</v>
+      </c>
+      <c r="B71" s="14">
+        <v>6</v>
+      </c>
+      <c r="C71" s="10">
+        <v>4</v>
+      </c>
+      <c r="D71" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E71">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="8">
+        <v>20</v>
+      </c>
+      <c r="B72" s="14">
+        <v>6</v>
+      </c>
+      <c r="C72" s="10">
+        <v>4</v>
+      </c>
+      <c r="D72" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E72">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="8">
+        <v>20</v>
+      </c>
+      <c r="B73" s="14">
+        <v>6</v>
+      </c>
+      <c r="C73" s="10">
+        <v>5</v>
+      </c>
+      <c r="D73" s="2">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="8">
+        <v>20</v>
+      </c>
+      <c r="B74" s="14">
+        <v>6</v>
+      </c>
+      <c r="C74" s="10">
+        <v>5</v>
+      </c>
+      <c r="D74" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E74">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="8">
+        <v>20</v>
+      </c>
+      <c r="B75" s="14">
+        <v>6</v>
+      </c>
+      <c r="C75" s="10">
+        <v>5</v>
+      </c>
+      <c r="D75" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E75">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="8">
+        <v>20</v>
+      </c>
+      <c r="B76" s="14">
+        <v>7</v>
+      </c>
+      <c r="C76" s="10">
+        <v>3</v>
+      </c>
+      <c r="D76" s="2">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="8">
+        <v>20</v>
+      </c>
+      <c r="B77" s="14">
+        <v>7</v>
+      </c>
+      <c r="C77" s="10">
+        <v>3</v>
+      </c>
+      <c r="D77" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E77">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="8">
+        <v>20</v>
+      </c>
+      <c r="B78" s="14">
+        <v>7</v>
+      </c>
+      <c r="C78" s="10">
+        <v>3</v>
+      </c>
+      <c r="D78" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E78">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="8">
+        <v>20</v>
+      </c>
+      <c r="B79" s="14">
+        <v>7</v>
+      </c>
+      <c r="C79" s="10">
+        <v>4</v>
+      </c>
+      <c r="D79" s="2">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="8">
+        <v>20</v>
+      </c>
+      <c r="B80" s="14">
+        <v>7</v>
+      </c>
+      <c r="C80" s="10">
+        <v>4</v>
+      </c>
+      <c r="D80" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="8">
+        <v>20</v>
+      </c>
+      <c r="B81" s="14">
+        <v>7</v>
+      </c>
+      <c r="C81" s="10">
+        <v>4</v>
+      </c>
+      <c r="D81" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="8">
+        <v>20</v>
+      </c>
+      <c r="B82" s="14">
+        <v>7</v>
+      </c>
+      <c r="C82" s="10">
+        <v>5</v>
+      </c>
+      <c r="D82" s="2">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="8">
+        <v>20</v>
+      </c>
+      <c r="B83" s="14">
+        <v>7</v>
+      </c>
+      <c r="C83" s="10">
+        <v>5</v>
+      </c>
+      <c r="D83" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E83">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="8">
+        <v>20</v>
+      </c>
+      <c r="B84" s="14">
+        <v>7</v>
+      </c>
+      <c r="C84" s="10">
+        <v>5</v>
+      </c>
+      <c r="D84" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E84">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F84">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="8">
+        <v>20</v>
+      </c>
+      <c r="B85" s="14">
+        <v>8</v>
+      </c>
+      <c r="C85" s="10">
+        <v>3</v>
+      </c>
+      <c r="D85" s="2">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F85">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="8">
+        <v>20</v>
+      </c>
+      <c r="B86" s="14">
+        <v>8</v>
+      </c>
+      <c r="C86" s="10">
+        <v>3</v>
+      </c>
+      <c r="D86" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E86">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="8">
+        <v>20</v>
+      </c>
+      <c r="B87" s="14">
+        <v>8</v>
+      </c>
+      <c r="C87" s="10">
+        <v>3</v>
+      </c>
+      <c r="D87" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="8">
+        <v>20</v>
+      </c>
+      <c r="B88" s="14">
+        <v>8</v>
+      </c>
+      <c r="C88" s="10">
+        <v>4</v>
+      </c>
+      <c r="D88" s="2">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F88">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="8">
+        <v>20</v>
+      </c>
+      <c r="B89" s="14">
+        <v>8</v>
+      </c>
+      <c r="C89" s="10">
+        <v>4</v>
+      </c>
+      <c r="D89" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E89">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F89">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="8">
+        <v>20</v>
+      </c>
+      <c r="B90" s="14">
+        <v>8</v>
+      </c>
+      <c r="C90" s="10">
+        <v>4</v>
+      </c>
+      <c r="D90" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E90">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="8">
+        <v>20</v>
+      </c>
+      <c r="B91" s="14">
+        <v>8</v>
+      </c>
+      <c r="C91" s="10">
+        <v>5</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="8">
+        <v>20</v>
+      </c>
+      <c r="B92" s="14">
+        <v>8</v>
+      </c>
+      <c r="C92" s="10">
+        <v>5</v>
+      </c>
+      <c r="D92" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="8">
+        <v>20</v>
+      </c>
+      <c r="B93" s="14">
+        <v>8</v>
+      </c>
+      <c r="C93" s="10">
+        <v>5</v>
+      </c>
+      <c r="D93" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E93">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="8">
+        <v>20</v>
+      </c>
+      <c r="B94" s="14">
         <v>9</v>
       </c>
-      <c r="C15" s="11">
-        <v>3</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>12.9</v>
-      </c>
-      <c r="G15" s="1">
-        <v>4557.1666670000004</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="9">
-        <v>20</v>
-      </c>
-      <c r="B16" s="12">
+      <c r="C94" s="10">
+        <v>3</v>
+      </c>
+      <c r="D94" s="2">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F94">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="8">
+        <v>20</v>
+      </c>
+      <c r="B95" s="14">
         <v>9</v>
       </c>
-      <c r="C16" s="11">
-        <v>3</v>
-      </c>
-      <c r="D16" s="5">
-        <v>4.45</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="1"/>
-        <v>12.9</v>
-      </c>
-      <c r="G16" s="1">
-        <v>4283.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
-        <v>20</v>
-      </c>
-      <c r="B17" s="12">
+      <c r="C95" s="10">
+        <v>3</v>
+      </c>
+      <c r="D95" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="8">
+        <v>20</v>
+      </c>
+      <c r="B96" s="14">
         <v>9</v>
       </c>
-      <c r="C17" s="11">
-        <v>4</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="0"/>
-        <v>19.2</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="1"/>
-        <v>14.4</v>
-      </c>
-      <c r="G17" s="1">
-        <v>4556.95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
-        <v>20</v>
-      </c>
-      <c r="B18" s="12">
+      <c r="C96" s="10">
+        <v>3</v>
+      </c>
+      <c r="D96" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E96">
+        <f t="shared" si="4"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="5"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="8">
+        <v>20</v>
+      </c>
+      <c r="B97" s="14">
         <v>9</v>
       </c>
-      <c r="C18" s="11">
-        <v>4</v>
-      </c>
-      <c r="D18" s="5">
-        <v>4.45</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="0"/>
-        <v>19.2</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="1"/>
-        <v>14.4</v>
-      </c>
-      <c r="G18" s="1">
-        <v>4283.5666670000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
-        <v>20</v>
-      </c>
-      <c r="B19" s="13">
-        <v>18</v>
-      </c>
-      <c r="C19" s="11">
-        <v>3</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="1"/>
-        <v>12.9</v>
-      </c>
-      <c r="G19" s="1">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
-        <v>20</v>
-      </c>
-      <c r="B20" s="13">
-        <v>18</v>
-      </c>
-      <c r="C20" s="11">
-        <v>3</v>
-      </c>
-      <c r="D20" s="5">
-        <v>4.45</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="1"/>
-        <v>12.9</v>
-      </c>
-      <c r="G20" s="1">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
-        <v>20</v>
-      </c>
-      <c r="B21" s="13">
-        <v>18</v>
-      </c>
-      <c r="C21" s="11">
-        <v>4</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="0"/>
-        <v>19.2</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="1"/>
-        <v>14.4</v>
-      </c>
-      <c r="G21" s="1">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
-        <v>20</v>
-      </c>
-      <c r="B22" s="13">
-        <v>18</v>
-      </c>
-      <c r="C22" s="11">
-        <v>4</v>
-      </c>
-      <c r="D22" s="5">
-        <v>4.45</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="0"/>
-        <v>19.2</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="1"/>
-        <v>14.4</v>
-      </c>
-      <c r="G22">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="14">
-        <v>35</v>
-      </c>
-      <c r="B23" s="10">
-        <v>5</v>
-      </c>
-      <c r="C23" s="11">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>12.9</v>
-      </c>
-      <c r="G23">
-        <v>2669.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="14">
-        <v>35</v>
-      </c>
-      <c r="B24" s="10">
-        <v>5</v>
-      </c>
-      <c r="C24" s="11">
-        <v>3</v>
-      </c>
-      <c r="D24" s="5">
-        <v>4.45</v>
-      </c>
-      <c r="E24">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="1"/>
-        <v>12.9</v>
-      </c>
-      <c r="G24">
-        <v>2428.6833329999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="14">
-        <v>35</v>
-      </c>
-      <c r="B25" s="10">
-        <v>5</v>
-      </c>
-      <c r="C25" s="11">
-        <v>4</v>
-      </c>
-      <c r="D25" s="2">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <f t="shared" si="0"/>
-        <v>19.2</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="1"/>
-        <v>14.4</v>
-      </c>
-      <c r="G25">
-        <v>2668.8666669999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="14">
-        <v>35</v>
-      </c>
-      <c r="B26" s="10">
-        <v>5</v>
-      </c>
-      <c r="C26" s="11">
-        <v>4</v>
-      </c>
-      <c r="D26" s="5">
-        <v>4.45</v>
-      </c>
-      <c r="E26">
-        <f t="shared" si="0"/>
-        <v>19.2</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="1"/>
-        <v>14.4</v>
-      </c>
-      <c r="G26">
-        <v>2428</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="14">
-        <v>35</v>
-      </c>
-      <c r="B27" s="15">
-        <v>16</v>
-      </c>
-      <c r="C27" s="11">
-        <v>3</v>
-      </c>
-      <c r="D27" s="2">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="1"/>
-        <v>12.9</v>
-      </c>
-      <c r="G27">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="14">
-        <v>35</v>
-      </c>
-      <c r="B28" s="15">
-        <v>16</v>
-      </c>
-      <c r="C28" s="11">
-        <v>3</v>
-      </c>
-      <c r="D28" s="5">
-        <v>4.45</v>
-      </c>
-      <c r="E28">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="1"/>
-        <v>12.9</v>
-      </c>
-      <c r="G28">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="14">
-        <v>35</v>
-      </c>
-      <c r="B29" s="15">
-        <v>16</v>
-      </c>
-      <c r="C29" s="11">
-        <v>4</v>
-      </c>
-      <c r="D29" s="2">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <f t="shared" si="0"/>
-        <v>19.2</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="1"/>
-        <v>14.4</v>
-      </c>
-      <c r="G29">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="14">
-        <v>35</v>
-      </c>
-      <c r="B30" s="15">
-        <v>16</v>
-      </c>
-      <c r="C30" s="11">
-        <v>4</v>
-      </c>
-      <c r="D30" s="5">
-        <v>4.45</v>
-      </c>
-      <c r="E30">
-        <f t="shared" si="0"/>
-        <v>19.2</v>
-      </c>
-      <c r="F30">
-        <f t="shared" si="1"/>
-        <v>14.4</v>
-      </c>
-      <c r="G30">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="14">
-        <v>35</v>
-      </c>
-      <c r="B31" s="16">
-        <v>32</v>
-      </c>
-      <c r="C31" s="11">
-        <v>3</v>
-      </c>
-      <c r="D31" s="2">
-        <v>0</v>
-      </c>
-      <c r="E31">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="F31">
-        <f t="shared" si="1"/>
-        <v>12.9</v>
-      </c>
-      <c r="G31">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="14">
-        <v>35</v>
-      </c>
-      <c r="B32" s="16">
-        <v>32</v>
-      </c>
-      <c r="C32" s="11">
-        <v>3</v>
-      </c>
-      <c r="D32" s="5">
-        <v>4.45</v>
-      </c>
-      <c r="E32">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="F32">
-        <f t="shared" si="1"/>
-        <v>12.9</v>
-      </c>
-      <c r="G32">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="14">
-        <v>35</v>
-      </c>
-      <c r="B33" s="16">
-        <v>32</v>
-      </c>
-      <c r="C33" s="11">
-        <v>4</v>
-      </c>
-      <c r="D33" s="2">
-        <v>0</v>
-      </c>
-      <c r="E33">
-        <f t="shared" si="0"/>
-        <v>19.2</v>
-      </c>
-      <c r="F33">
-        <f t="shared" si="1"/>
-        <v>14.4</v>
-      </c>
-      <c r="G33">
-        <v>8760</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="14">
-        <v>35</v>
-      </c>
-      <c r="B34" s="16">
-        <v>32</v>
-      </c>
-      <c r="C34" s="11">
-        <v>4</v>
-      </c>
-      <c r="D34" s="5">
-        <v>4.45</v>
-      </c>
-      <c r="E34">
-        <f t="shared" si="0"/>
-        <v>19.2</v>
-      </c>
-      <c r="F34">
-        <f t="shared" si="1"/>
-        <v>14.4</v>
-      </c>
-      <c r="G34">
-        <v>8760</v>
+      <c r="C97" s="10">
+        <v>4</v>
+      </c>
+      <c r="D97" s="2">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <f t="shared" si="4"/>
+        <v>19.2</v>
+      </c>
+      <c r="F97">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="8">
+        <v>20</v>
+      </c>
+      <c r="B98" s="14">
+        <v>9</v>
+      </c>
+      <c r="C98" s="10">
+        <v>4</v>
+      </c>
+      <c r="D98" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E98">
+        <f t="shared" ref="E98:E161" si="6">C98*4.8</f>
+        <v>19.2</v>
+      </c>
+      <c r="F98">
+        <f t="shared" ref="F98:F161" si="7">IF(C98=0, 0, IF(C98&gt;3, 14.4, IF(C98=2, 8.6, 12.9)))</f>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="8">
+        <v>20</v>
+      </c>
+      <c r="B99" s="14">
+        <v>9</v>
+      </c>
+      <c r="C99" s="10">
+        <v>4</v>
+      </c>
+      <c r="D99" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E99">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F99">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="8">
+        <v>20</v>
+      </c>
+      <c r="B100" s="14">
+        <v>9</v>
+      </c>
+      <c r="C100" s="10">
+        <v>5</v>
+      </c>
+      <c r="D100" s="2">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F100">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="8">
+        <v>20</v>
+      </c>
+      <c r="B101" s="14">
+        <v>9</v>
+      </c>
+      <c r="C101" s="10">
+        <v>5</v>
+      </c>
+      <c r="D101" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E101">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F101">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="8">
+        <v>20</v>
+      </c>
+      <c r="B102" s="14">
+        <v>9</v>
+      </c>
+      <c r="C102" s="10">
+        <v>5</v>
+      </c>
+      <c r="D102" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E102">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F102">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="8">
+        <v>20</v>
+      </c>
+      <c r="B103" s="14">
+        <v>10</v>
+      </c>
+      <c r="C103" s="10">
+        <v>3</v>
+      </c>
+      <c r="D103" s="2">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F103">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="8">
+        <v>20</v>
+      </c>
+      <c r="B104" s="14">
+        <v>10</v>
+      </c>
+      <c r="C104" s="10">
+        <v>3</v>
+      </c>
+      <c r="D104" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E104">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F104">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="8">
+        <v>20</v>
+      </c>
+      <c r="B105" s="14">
+        <v>10</v>
+      </c>
+      <c r="C105" s="10">
+        <v>3</v>
+      </c>
+      <c r="D105" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E105">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F105">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="8">
+        <v>20</v>
+      </c>
+      <c r="B106" s="14">
+        <v>10</v>
+      </c>
+      <c r="C106" s="10">
+        <v>4</v>
+      </c>
+      <c r="D106" s="2">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F106">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="8">
+        <v>20</v>
+      </c>
+      <c r="B107" s="14">
+        <v>10</v>
+      </c>
+      <c r="C107" s="10">
+        <v>4</v>
+      </c>
+      <c r="D107" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E107">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F107">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="8">
+        <v>20</v>
+      </c>
+      <c r="B108" s="14">
+        <v>10</v>
+      </c>
+      <c r="C108" s="10">
+        <v>4</v>
+      </c>
+      <c r="D108" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E108">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F108">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="8">
+        <v>20</v>
+      </c>
+      <c r="B109" s="14">
+        <v>10</v>
+      </c>
+      <c r="C109" s="10">
+        <v>5</v>
+      </c>
+      <c r="D109" s="2">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F109">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="8">
+        <v>20</v>
+      </c>
+      <c r="B110" s="14">
+        <v>10</v>
+      </c>
+      <c r="C110" s="10">
+        <v>5</v>
+      </c>
+      <c r="D110" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E110">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F110">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="8">
+        <v>20</v>
+      </c>
+      <c r="B111" s="14">
+        <v>10</v>
+      </c>
+      <c r="C111" s="10">
+        <v>5</v>
+      </c>
+      <c r="D111" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E111">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F111">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="8">
+        <v>20</v>
+      </c>
+      <c r="B112" s="14">
+        <v>11</v>
+      </c>
+      <c r="C112" s="10">
+        <v>3</v>
+      </c>
+      <c r="D112" s="2">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F112">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="8">
+        <v>20</v>
+      </c>
+      <c r="B113" s="14">
+        <v>11</v>
+      </c>
+      <c r="C113" s="10">
+        <v>3</v>
+      </c>
+      <c r="D113" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E113">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F113">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="8">
+        <v>20</v>
+      </c>
+      <c r="B114" s="14">
+        <v>11</v>
+      </c>
+      <c r="C114" s="10">
+        <v>3</v>
+      </c>
+      <c r="D114" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E114">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F114">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="8">
+        <v>20</v>
+      </c>
+      <c r="B115" s="14">
+        <v>11</v>
+      </c>
+      <c r="C115" s="10">
+        <v>4</v>
+      </c>
+      <c r="D115" s="2">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F115">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="8">
+        <v>20</v>
+      </c>
+      <c r="B116" s="14">
+        <v>11</v>
+      </c>
+      <c r="C116" s="10">
+        <v>4</v>
+      </c>
+      <c r="D116" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E116">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F116">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="8">
+        <v>20</v>
+      </c>
+      <c r="B117" s="14">
+        <v>11</v>
+      </c>
+      <c r="C117" s="10">
+        <v>4</v>
+      </c>
+      <c r="D117" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E117">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F117">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="8">
+        <v>20</v>
+      </c>
+      <c r="B118" s="14">
+        <v>11</v>
+      </c>
+      <c r="C118" s="10">
+        <v>5</v>
+      </c>
+      <c r="D118" s="2">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F118">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="8">
+        <v>20</v>
+      </c>
+      <c r="B119" s="14">
+        <v>11</v>
+      </c>
+      <c r="C119" s="10">
+        <v>5</v>
+      </c>
+      <c r="D119" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E119">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F119">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="8">
+        <v>20</v>
+      </c>
+      <c r="B120" s="14">
+        <v>11</v>
+      </c>
+      <c r="C120" s="10">
+        <v>5</v>
+      </c>
+      <c r="D120" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E120">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F120">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="8">
+        <v>20</v>
+      </c>
+      <c r="B121" s="14">
+        <v>12</v>
+      </c>
+      <c r="C121" s="10">
+        <v>3</v>
+      </c>
+      <c r="D121" s="2">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F121">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="8">
+        <v>20</v>
+      </c>
+      <c r="B122" s="14">
+        <v>12</v>
+      </c>
+      <c r="C122" s="10">
+        <v>3</v>
+      </c>
+      <c r="D122" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E122">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F122">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="8">
+        <v>20</v>
+      </c>
+      <c r="B123" s="14">
+        <v>12</v>
+      </c>
+      <c r="C123" s="10">
+        <v>3</v>
+      </c>
+      <c r="D123" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E123">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F123">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="8">
+        <v>20</v>
+      </c>
+      <c r="B124" s="14">
+        <v>12</v>
+      </c>
+      <c r="C124" s="10">
+        <v>4</v>
+      </c>
+      <c r="D124" s="2">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F124">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="8">
+        <v>20</v>
+      </c>
+      <c r="B125" s="14">
+        <v>12</v>
+      </c>
+      <c r="C125" s="10">
+        <v>4</v>
+      </c>
+      <c r="D125" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E125">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F125">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="8">
+        <v>20</v>
+      </c>
+      <c r="B126" s="14">
+        <v>12</v>
+      </c>
+      <c r="C126" s="10">
+        <v>4</v>
+      </c>
+      <c r="D126" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E126">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F126">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="8">
+        <v>20</v>
+      </c>
+      <c r="B127" s="14">
+        <v>12</v>
+      </c>
+      <c r="C127" s="10">
+        <v>5</v>
+      </c>
+      <c r="D127" s="2">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F127">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="8">
+        <v>20</v>
+      </c>
+      <c r="B128" s="14">
+        <v>12</v>
+      </c>
+      <c r="C128" s="10">
+        <v>5</v>
+      </c>
+      <c r="D128" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E128">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F128">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="8">
+        <v>20</v>
+      </c>
+      <c r="B129" s="14">
+        <v>12</v>
+      </c>
+      <c r="C129" s="10">
+        <v>5</v>
+      </c>
+      <c r="D129" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E129">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F129">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="8">
+        <v>35</v>
+      </c>
+      <c r="B130" s="9">
+        <v>1</v>
+      </c>
+      <c r="C130" s="10">
+        <v>3</v>
+      </c>
+      <c r="D130" s="2">
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F130">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="8">
+        <v>35</v>
+      </c>
+      <c r="B131" s="9">
+        <v>1</v>
+      </c>
+      <c r="C131" s="10">
+        <v>3</v>
+      </c>
+      <c r="D131" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E131">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F131">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="8">
+        <v>35</v>
+      </c>
+      <c r="B132" s="9">
+        <v>1</v>
+      </c>
+      <c r="C132" s="10">
+        <v>3</v>
+      </c>
+      <c r="D132" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E132">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F132">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="8">
+        <v>35</v>
+      </c>
+      <c r="B133" s="9">
+        <v>1</v>
+      </c>
+      <c r="C133" s="10">
+        <v>4</v>
+      </c>
+      <c r="D133" s="2">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F133">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="8">
+        <v>35</v>
+      </c>
+      <c r="B134" s="11">
+        <v>1</v>
+      </c>
+      <c r="C134" s="10">
+        <v>4</v>
+      </c>
+      <c r="D134" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E134">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F134">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="8">
+        <v>35</v>
+      </c>
+      <c r="B135" s="11">
+        <v>1</v>
+      </c>
+      <c r="C135" s="10">
+        <v>4</v>
+      </c>
+      <c r="D135" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E135">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F135">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="8">
+        <v>35</v>
+      </c>
+      <c r="B136" s="11">
+        <v>1</v>
+      </c>
+      <c r="C136" s="10">
+        <v>5</v>
+      </c>
+      <c r="D136" s="2">
+        <v>0</v>
+      </c>
+      <c r="E136">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F136">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="8">
+        <v>35</v>
+      </c>
+      <c r="B137" s="11">
+        <v>1</v>
+      </c>
+      <c r="C137" s="10">
+        <v>5</v>
+      </c>
+      <c r="D137" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E137">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F137">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="8">
+        <v>35</v>
+      </c>
+      <c r="B138" s="12">
+        <v>1</v>
+      </c>
+      <c r="C138" s="10">
+        <v>5</v>
+      </c>
+      <c r="D138" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E138">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F138">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="8">
+        <v>35</v>
+      </c>
+      <c r="B139" s="9">
+        <v>2</v>
+      </c>
+      <c r="C139" s="10">
+        <v>3</v>
+      </c>
+      <c r="D139" s="2">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F139">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="8">
+        <v>35</v>
+      </c>
+      <c r="B140" s="9">
+        <v>2</v>
+      </c>
+      <c r="C140" s="10">
+        <v>3</v>
+      </c>
+      <c r="D140" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E140">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F140">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="8">
+        <v>35</v>
+      </c>
+      <c r="B141" s="9">
+        <v>2</v>
+      </c>
+      <c r="C141" s="10">
+        <v>3</v>
+      </c>
+      <c r="D141" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E141">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F141">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="8">
+        <v>35</v>
+      </c>
+      <c r="B142" s="9">
+        <v>2</v>
+      </c>
+      <c r="C142" s="10">
+        <v>4</v>
+      </c>
+      <c r="D142" s="2">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F142">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="8">
+        <v>35</v>
+      </c>
+      <c r="B143" s="9">
+        <v>2</v>
+      </c>
+      <c r="C143" s="10">
+        <v>4</v>
+      </c>
+      <c r="D143" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E143">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F143">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="8">
+        <v>35</v>
+      </c>
+      <c r="B144" s="9">
+        <v>2</v>
+      </c>
+      <c r="C144" s="10">
+        <v>4</v>
+      </c>
+      <c r="D144" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E144">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F144">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="8">
+        <v>35</v>
+      </c>
+      <c r="B145" s="9">
+        <v>2</v>
+      </c>
+      <c r="C145" s="10">
+        <v>5</v>
+      </c>
+      <c r="D145" s="2">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F145">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="8">
+        <v>35</v>
+      </c>
+      <c r="B146" s="9">
+        <v>2</v>
+      </c>
+      <c r="C146" s="10">
+        <v>5</v>
+      </c>
+      <c r="D146" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E146">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F146">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="8">
+        <v>35</v>
+      </c>
+      <c r="B147" s="9">
+        <v>2</v>
+      </c>
+      <c r="C147" s="10">
+        <v>5</v>
+      </c>
+      <c r="D147" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E147">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F147">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="8">
+        <v>35</v>
+      </c>
+      <c r="B148" s="9">
+        <v>3</v>
+      </c>
+      <c r="C148" s="10">
+        <v>3</v>
+      </c>
+      <c r="D148" s="2">
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F148">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="8">
+        <v>35</v>
+      </c>
+      <c r="B149" s="9">
+        <v>3</v>
+      </c>
+      <c r="C149" s="10">
+        <v>3</v>
+      </c>
+      <c r="D149" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E149">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F149">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="8">
+        <v>35</v>
+      </c>
+      <c r="B150" s="9">
+        <v>3</v>
+      </c>
+      <c r="C150" s="10">
+        <v>3</v>
+      </c>
+      <c r="D150" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E150">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F150">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="8">
+        <v>35</v>
+      </c>
+      <c r="B151" s="9">
+        <v>3</v>
+      </c>
+      <c r="C151" s="10">
+        <v>4</v>
+      </c>
+      <c r="D151" s="2">
+        <v>0</v>
+      </c>
+      <c r="E151">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F151">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="8">
+        <v>35</v>
+      </c>
+      <c r="B152" s="9">
+        <v>3</v>
+      </c>
+      <c r="C152" s="10">
+        <v>4</v>
+      </c>
+      <c r="D152" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E152">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F152">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="8">
+        <v>35</v>
+      </c>
+      <c r="B153" s="9">
+        <v>3</v>
+      </c>
+      <c r="C153" s="10">
+        <v>4</v>
+      </c>
+      <c r="D153" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E153">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F153">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="8">
+        <v>35</v>
+      </c>
+      <c r="B154" s="9">
+        <v>3</v>
+      </c>
+      <c r="C154" s="10">
+        <v>5</v>
+      </c>
+      <c r="D154" s="2">
+        <v>0</v>
+      </c>
+      <c r="E154">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F154">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="8">
+        <v>35</v>
+      </c>
+      <c r="B155" s="9">
+        <v>3</v>
+      </c>
+      <c r="C155" s="10">
+        <v>5</v>
+      </c>
+      <c r="D155" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E155">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F155">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="8">
+        <v>35</v>
+      </c>
+      <c r="B156" s="9">
+        <v>3</v>
+      </c>
+      <c r="C156" s="10">
+        <v>5</v>
+      </c>
+      <c r="D156" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E156">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="F156">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="8">
+        <v>35</v>
+      </c>
+      <c r="B157" s="14">
+        <v>4</v>
+      </c>
+      <c r="C157" s="10">
+        <v>3</v>
+      </c>
+      <c r="D157" s="2">
+        <v>0</v>
+      </c>
+      <c r="E157">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F157">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="8">
+        <v>35</v>
+      </c>
+      <c r="B158" s="14">
+        <v>4</v>
+      </c>
+      <c r="C158" s="10">
+        <v>3</v>
+      </c>
+      <c r="D158" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E158">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F158">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="8">
+        <v>35</v>
+      </c>
+      <c r="B159" s="14">
+        <v>4</v>
+      </c>
+      <c r="C159" s="10">
+        <v>3</v>
+      </c>
+      <c r="D159" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E159">
+        <f t="shared" si="6"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F159">
+        <f t="shared" si="7"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="8">
+        <v>35</v>
+      </c>
+      <c r="B160" s="14">
+        <v>4</v>
+      </c>
+      <c r="C160" s="10">
+        <v>4</v>
+      </c>
+      <c r="D160" s="2">
+        <v>0</v>
+      </c>
+      <c r="E160">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F160">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="8">
+        <v>35</v>
+      </c>
+      <c r="B161" s="14">
+        <v>4</v>
+      </c>
+      <c r="C161" s="10">
+        <v>4</v>
+      </c>
+      <c r="D161" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E161">
+        <f t="shared" si="6"/>
+        <v>19.2</v>
+      </c>
+      <c r="F161">
+        <f t="shared" si="7"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="8">
+        <v>35</v>
+      </c>
+      <c r="B162" s="14">
+        <v>4</v>
+      </c>
+      <c r="C162" s="10">
+        <v>4</v>
+      </c>
+      <c r="D162" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E162">
+        <f t="shared" ref="E162:E225" si="8">C162*4.8</f>
+        <v>19.2</v>
+      </c>
+      <c r="F162">
+        <f t="shared" ref="F162:F225" si="9">IF(C162=0, 0, IF(C162&gt;3, 14.4, IF(C162=2, 8.6, 12.9)))</f>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="8">
+        <v>35</v>
+      </c>
+      <c r="B163" s="14">
+        <v>4</v>
+      </c>
+      <c r="C163" s="10">
+        <v>5</v>
+      </c>
+      <c r="D163" s="2">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F163">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="8">
+        <v>35</v>
+      </c>
+      <c r="B164" s="14">
+        <v>4</v>
+      </c>
+      <c r="C164" s="10">
+        <v>5</v>
+      </c>
+      <c r="D164" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E164">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F164">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="8">
+        <v>35</v>
+      </c>
+      <c r="B165" s="14">
+        <v>4</v>
+      </c>
+      <c r="C165" s="10">
+        <v>5</v>
+      </c>
+      <c r="D165" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E165">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F165">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="8">
+        <v>35</v>
+      </c>
+      <c r="B166" s="14">
+        <v>5</v>
+      </c>
+      <c r="C166" s="10">
+        <v>3</v>
+      </c>
+      <c r="D166" s="2">
+        <v>0</v>
+      </c>
+      <c r="E166">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F166">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="8">
+        <v>35</v>
+      </c>
+      <c r="B167" s="14">
+        <v>5</v>
+      </c>
+      <c r="C167" s="10">
+        <v>3</v>
+      </c>
+      <c r="D167" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E167">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F167">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="8">
+        <v>35</v>
+      </c>
+      <c r="B168" s="14">
+        <v>5</v>
+      </c>
+      <c r="C168" s="10">
+        <v>3</v>
+      </c>
+      <c r="D168" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E168">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F168">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="8">
+        <v>35</v>
+      </c>
+      <c r="B169" s="14">
+        <v>5</v>
+      </c>
+      <c r="C169" s="10">
+        <v>4</v>
+      </c>
+      <c r="D169" s="2">
+        <v>0</v>
+      </c>
+      <c r="E169">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F169">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="8">
+        <v>35</v>
+      </c>
+      <c r="B170" s="14">
+        <v>5</v>
+      </c>
+      <c r="C170" s="10">
+        <v>4</v>
+      </c>
+      <c r="D170" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E170">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F170">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="8">
+        <v>35</v>
+      </c>
+      <c r="B171" s="14">
+        <v>5</v>
+      </c>
+      <c r="C171" s="10">
+        <v>4</v>
+      </c>
+      <c r="D171" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E171">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F171">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="8">
+        <v>35</v>
+      </c>
+      <c r="B172" s="14">
+        <v>5</v>
+      </c>
+      <c r="C172" s="10">
+        <v>5</v>
+      </c>
+      <c r="D172" s="2">
+        <v>0</v>
+      </c>
+      <c r="E172">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F172">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="8">
+        <v>35</v>
+      </c>
+      <c r="B173" s="14">
+        <v>5</v>
+      </c>
+      <c r="C173" s="10">
+        <v>5</v>
+      </c>
+      <c r="D173" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E173">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F173">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="8">
+        <v>35</v>
+      </c>
+      <c r="B174" s="14">
+        <v>5</v>
+      </c>
+      <c r="C174" s="10">
+        <v>5</v>
+      </c>
+      <c r="D174" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E174">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F174">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="8">
+        <v>35</v>
+      </c>
+      <c r="B175" s="14">
+        <v>6</v>
+      </c>
+      <c r="C175" s="10">
+        <v>3</v>
+      </c>
+      <c r="D175" s="2">
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F175">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" s="8">
+        <v>35</v>
+      </c>
+      <c r="B176" s="14">
+        <v>6</v>
+      </c>
+      <c r="C176" s="10">
+        <v>3</v>
+      </c>
+      <c r="D176" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E176">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F176">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="8">
+        <v>35</v>
+      </c>
+      <c r="B177" s="14">
+        <v>6</v>
+      </c>
+      <c r="C177" s="10">
+        <v>3</v>
+      </c>
+      <c r="D177" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E177">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F177">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="8">
+        <v>35</v>
+      </c>
+      <c r="B178" s="14">
+        <v>6</v>
+      </c>
+      <c r="C178" s="10">
+        <v>4</v>
+      </c>
+      <c r="D178" s="2">
+        <v>0</v>
+      </c>
+      <c r="E178">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F178">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" s="8">
+        <v>35</v>
+      </c>
+      <c r="B179" s="14">
+        <v>6</v>
+      </c>
+      <c r="C179" s="10">
+        <v>4</v>
+      </c>
+      <c r="D179" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E179">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F179">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="8">
+        <v>35</v>
+      </c>
+      <c r="B180" s="14">
+        <v>6</v>
+      </c>
+      <c r="C180" s="10">
+        <v>4</v>
+      </c>
+      <c r="D180" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E180">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F180">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="8">
+        <v>35</v>
+      </c>
+      <c r="B181" s="14">
+        <v>6</v>
+      </c>
+      <c r="C181" s="10">
+        <v>5</v>
+      </c>
+      <c r="D181" s="2">
+        <v>0</v>
+      </c>
+      <c r="E181">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F181">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" s="8">
+        <v>35</v>
+      </c>
+      <c r="B182" s="14">
+        <v>6</v>
+      </c>
+      <c r="C182" s="10">
+        <v>5</v>
+      </c>
+      <c r="D182" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E182">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F182">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="8">
+        <v>35</v>
+      </c>
+      <c r="B183" s="14">
+        <v>6</v>
+      </c>
+      <c r="C183" s="10">
+        <v>5</v>
+      </c>
+      <c r="D183" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E183">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F183">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="8">
+        <v>35</v>
+      </c>
+      <c r="B184" s="14">
+        <v>7</v>
+      </c>
+      <c r="C184" s="10">
+        <v>3</v>
+      </c>
+      <c r="D184" s="2">
+        <v>0</v>
+      </c>
+      <c r="E184">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F184">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="8">
+        <v>35</v>
+      </c>
+      <c r="B185" s="14">
+        <v>7</v>
+      </c>
+      <c r="C185" s="10">
+        <v>3</v>
+      </c>
+      <c r="D185" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E185">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F185">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="8">
+        <v>35</v>
+      </c>
+      <c r="B186" s="14">
+        <v>7</v>
+      </c>
+      <c r="C186" s="10">
+        <v>3</v>
+      </c>
+      <c r="D186" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E186">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F186">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="8">
+        <v>35</v>
+      </c>
+      <c r="B187" s="14">
+        <v>7</v>
+      </c>
+      <c r="C187" s="10">
+        <v>4</v>
+      </c>
+      <c r="D187" s="2">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F187">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="8">
+        <v>35</v>
+      </c>
+      <c r="B188" s="14">
+        <v>7</v>
+      </c>
+      <c r="C188" s="10">
+        <v>4</v>
+      </c>
+      <c r="D188" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E188">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F188">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="8">
+        <v>35</v>
+      </c>
+      <c r="B189" s="14">
+        <v>7</v>
+      </c>
+      <c r="C189" s="10">
+        <v>4</v>
+      </c>
+      <c r="D189" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E189">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F189">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="8">
+        <v>35</v>
+      </c>
+      <c r="B190" s="14">
+        <v>7</v>
+      </c>
+      <c r="C190" s="10">
+        <v>5</v>
+      </c>
+      <c r="D190" s="2">
+        <v>0</v>
+      </c>
+      <c r="E190">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F190">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="8">
+        <v>35</v>
+      </c>
+      <c r="B191" s="14">
+        <v>7</v>
+      </c>
+      <c r="C191" s="10">
+        <v>5</v>
+      </c>
+      <c r="D191" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E191">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F191">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="8">
+        <v>35</v>
+      </c>
+      <c r="B192" s="14">
+        <v>7</v>
+      </c>
+      <c r="C192" s="10">
+        <v>5</v>
+      </c>
+      <c r="D192" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E192">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F192">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" s="8">
+        <v>35</v>
+      </c>
+      <c r="B193" s="14">
+        <v>8</v>
+      </c>
+      <c r="C193" s="10">
+        <v>3</v>
+      </c>
+      <c r="D193" s="2">
+        <v>0</v>
+      </c>
+      <c r="E193">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F193">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" s="8">
+        <v>35</v>
+      </c>
+      <c r="B194" s="14">
+        <v>8</v>
+      </c>
+      <c r="C194" s="10">
+        <v>3</v>
+      </c>
+      <c r="D194" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E194">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F194">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" s="8">
+        <v>35</v>
+      </c>
+      <c r="B195" s="14">
+        <v>8</v>
+      </c>
+      <c r="C195" s="10">
+        <v>3</v>
+      </c>
+      <c r="D195" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E195">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F195">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" s="8">
+        <v>35</v>
+      </c>
+      <c r="B196" s="14">
+        <v>8</v>
+      </c>
+      <c r="C196" s="10">
+        <v>4</v>
+      </c>
+      <c r="D196" s="2">
+        <v>0</v>
+      </c>
+      <c r="E196">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F196">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" s="8">
+        <v>35</v>
+      </c>
+      <c r="B197" s="14">
+        <v>8</v>
+      </c>
+      <c r="C197" s="10">
+        <v>4</v>
+      </c>
+      <c r="D197" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E197">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F197">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" s="8">
+        <v>35</v>
+      </c>
+      <c r="B198" s="14">
+        <v>8</v>
+      </c>
+      <c r="C198" s="10">
+        <v>4</v>
+      </c>
+      <c r="D198" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E198">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F198">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" s="8">
+        <v>35</v>
+      </c>
+      <c r="B199" s="14">
+        <v>8</v>
+      </c>
+      <c r="C199" s="10">
+        <v>5</v>
+      </c>
+      <c r="D199" s="2">
+        <v>0</v>
+      </c>
+      <c r="E199">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F199">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="8">
+        <v>35</v>
+      </c>
+      <c r="B200" s="14">
+        <v>8</v>
+      </c>
+      <c r="C200" s="10">
+        <v>5</v>
+      </c>
+      <c r="D200" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E200">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F200">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="8">
+        <v>35</v>
+      </c>
+      <c r="B201" s="14">
+        <v>8</v>
+      </c>
+      <c r="C201" s="10">
+        <v>5</v>
+      </c>
+      <c r="D201" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E201">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F201">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="8">
+        <v>35</v>
+      </c>
+      <c r="B202" s="14">
+        <v>9</v>
+      </c>
+      <c r="C202" s="10">
+        <v>3</v>
+      </c>
+      <c r="D202" s="2">
+        <v>0</v>
+      </c>
+      <c r="E202">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F202">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="8">
+        <v>35</v>
+      </c>
+      <c r="B203" s="14">
+        <v>9</v>
+      </c>
+      <c r="C203" s="10">
+        <v>3</v>
+      </c>
+      <c r="D203" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E203">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F203">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" s="8">
+        <v>35</v>
+      </c>
+      <c r="B204" s="14">
+        <v>9</v>
+      </c>
+      <c r="C204" s="10">
+        <v>3</v>
+      </c>
+      <c r="D204" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E204">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F204">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" s="8">
+        <v>35</v>
+      </c>
+      <c r="B205" s="14">
+        <v>9</v>
+      </c>
+      <c r="C205" s="10">
+        <v>4</v>
+      </c>
+      <c r="D205" s="2">
+        <v>0</v>
+      </c>
+      <c r="E205">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F205">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" s="8">
+        <v>35</v>
+      </c>
+      <c r="B206" s="14">
+        <v>9</v>
+      </c>
+      <c r="C206" s="10">
+        <v>4</v>
+      </c>
+      <c r="D206" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E206">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F206">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" s="8">
+        <v>35</v>
+      </c>
+      <c r="B207" s="14">
+        <v>9</v>
+      </c>
+      <c r="C207" s="10">
+        <v>4</v>
+      </c>
+      <c r="D207" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E207">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F207">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" s="8">
+        <v>35</v>
+      </c>
+      <c r="B208" s="14">
+        <v>9</v>
+      </c>
+      <c r="C208" s="10">
+        <v>5</v>
+      </c>
+      <c r="D208" s="2">
+        <v>0</v>
+      </c>
+      <c r="E208">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F208">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" s="8">
+        <v>35</v>
+      </c>
+      <c r="B209" s="14">
+        <v>9</v>
+      </c>
+      <c r="C209" s="10">
+        <v>5</v>
+      </c>
+      <c r="D209" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E209">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F209">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" s="8">
+        <v>35</v>
+      </c>
+      <c r="B210" s="14">
+        <v>9</v>
+      </c>
+      <c r="C210" s="10">
+        <v>5</v>
+      </c>
+      <c r="D210" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E210">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F210">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" s="8">
+        <v>35</v>
+      </c>
+      <c r="B211" s="14">
+        <v>10</v>
+      </c>
+      <c r="C211" s="10">
+        <v>3</v>
+      </c>
+      <c r="D211" s="2">
+        <v>0</v>
+      </c>
+      <c r="E211">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F211">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" s="8">
+        <v>35</v>
+      </c>
+      <c r="B212" s="14">
+        <v>10</v>
+      </c>
+      <c r="C212" s="10">
+        <v>3</v>
+      </c>
+      <c r="D212" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E212">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F212">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" s="8">
+        <v>35</v>
+      </c>
+      <c r="B213" s="14">
+        <v>10</v>
+      </c>
+      <c r="C213" s="10">
+        <v>3</v>
+      </c>
+      <c r="D213" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E213">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F213">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" s="8">
+        <v>35</v>
+      </c>
+      <c r="B214" s="14">
+        <v>10</v>
+      </c>
+      <c r="C214" s="10">
+        <v>4</v>
+      </c>
+      <c r="D214" s="2">
+        <v>0</v>
+      </c>
+      <c r="E214">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F214">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" s="8">
+        <v>35</v>
+      </c>
+      <c r="B215" s="14">
+        <v>10</v>
+      </c>
+      <c r="C215" s="10">
+        <v>4</v>
+      </c>
+      <c r="D215" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E215">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F215">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" s="8">
+        <v>35</v>
+      </c>
+      <c r="B216" s="14">
+        <v>10</v>
+      </c>
+      <c r="C216" s="10">
+        <v>4</v>
+      </c>
+      <c r="D216" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E216">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F216">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" s="8">
+        <v>35</v>
+      </c>
+      <c r="B217" s="14">
+        <v>10</v>
+      </c>
+      <c r="C217" s="10">
+        <v>5</v>
+      </c>
+      <c r="D217" s="2">
+        <v>0</v>
+      </c>
+      <c r="E217">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F217">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" s="8">
+        <v>35</v>
+      </c>
+      <c r="B218" s="14">
+        <v>10</v>
+      </c>
+      <c r="C218" s="10">
+        <v>5</v>
+      </c>
+      <c r="D218" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E218">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F218">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" s="8">
+        <v>35</v>
+      </c>
+      <c r="B219" s="14">
+        <v>10</v>
+      </c>
+      <c r="C219" s="10">
+        <v>5</v>
+      </c>
+      <c r="D219" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E219">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="F219">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" s="8">
+        <v>35</v>
+      </c>
+      <c r="B220" s="14">
+        <v>11</v>
+      </c>
+      <c r="C220" s="10">
+        <v>3</v>
+      </c>
+      <c r="D220" s="2">
+        <v>0</v>
+      </c>
+      <c r="E220">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F220">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" s="8">
+        <v>35</v>
+      </c>
+      <c r="B221" s="14">
+        <v>11</v>
+      </c>
+      <c r="C221" s="10">
+        <v>3</v>
+      </c>
+      <c r="D221" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E221">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F221">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" s="8">
+        <v>35</v>
+      </c>
+      <c r="B222" s="14">
+        <v>11</v>
+      </c>
+      <c r="C222" s="10">
+        <v>3</v>
+      </c>
+      <c r="D222" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E222">
+        <f t="shared" si="8"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F222">
+        <f t="shared" si="9"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" s="8">
+        <v>35</v>
+      </c>
+      <c r="B223" s="14">
+        <v>11</v>
+      </c>
+      <c r="C223" s="10">
+        <v>4</v>
+      </c>
+      <c r="D223" s="2">
+        <v>0</v>
+      </c>
+      <c r="E223">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F223">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" s="8">
+        <v>35</v>
+      </c>
+      <c r="B224" s="14">
+        <v>11</v>
+      </c>
+      <c r="C224" s="10">
+        <v>4</v>
+      </c>
+      <c r="D224" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E224">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F224">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" s="8">
+        <v>35</v>
+      </c>
+      <c r="B225" s="14">
+        <v>11</v>
+      </c>
+      <c r="C225" s="10">
+        <v>4</v>
+      </c>
+      <c r="D225" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E225">
+        <f t="shared" si="8"/>
+        <v>19.2</v>
+      </c>
+      <c r="F225">
+        <f t="shared" si="9"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" s="8">
+        <v>35</v>
+      </c>
+      <c r="B226" s="14">
+        <v>11</v>
+      </c>
+      <c r="C226" s="10">
+        <v>5</v>
+      </c>
+      <c r="D226" s="2">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <f t="shared" ref="E226:E237" si="10">C226*4.8</f>
+        <v>24</v>
+      </c>
+      <c r="F226">
+        <f t="shared" ref="F226:F237" si="11">IF(C226=0, 0, IF(C226&gt;3, 14.4, IF(C226=2, 8.6, 12.9)))</f>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" s="8">
+        <v>35</v>
+      </c>
+      <c r="B227" s="14">
+        <v>11</v>
+      </c>
+      <c r="C227" s="10">
+        <v>5</v>
+      </c>
+      <c r="D227" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E227">
+        <f t="shared" si="10"/>
+        <v>24</v>
+      </c>
+      <c r="F227">
+        <f t="shared" si="11"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228" s="8">
+        <v>35</v>
+      </c>
+      <c r="B228" s="14">
+        <v>11</v>
+      </c>
+      <c r="C228" s="10">
+        <v>5</v>
+      </c>
+      <c r="D228" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E228">
+        <f t="shared" si="10"/>
+        <v>24</v>
+      </c>
+      <c r="F228">
+        <f t="shared" si="11"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A229" s="8">
+        <v>35</v>
+      </c>
+      <c r="B229" s="14">
+        <v>12</v>
+      </c>
+      <c r="C229" s="10">
+        <v>3</v>
+      </c>
+      <c r="D229" s="2">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <f t="shared" si="10"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F229">
+        <f t="shared" si="11"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" s="8">
+        <v>35</v>
+      </c>
+      <c r="B230" s="14">
+        <v>12</v>
+      </c>
+      <c r="C230" s="10">
+        <v>3</v>
+      </c>
+      <c r="D230" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E230">
+        <f t="shared" si="10"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F230">
+        <f t="shared" si="11"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" s="8">
+        <v>35</v>
+      </c>
+      <c r="B231" s="14">
+        <v>12</v>
+      </c>
+      <c r="C231" s="10">
+        <v>3</v>
+      </c>
+      <c r="D231" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E231">
+        <f t="shared" si="10"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="F231">
+        <f t="shared" si="11"/>
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" s="8">
+        <v>35</v>
+      </c>
+      <c r="B232" s="14">
+        <v>12</v>
+      </c>
+      <c r="C232" s="10">
+        <v>4</v>
+      </c>
+      <c r="D232" s="2">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <f t="shared" si="10"/>
+        <v>19.2</v>
+      </c>
+      <c r="F232">
+        <f t="shared" si="11"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" s="8">
+        <v>35</v>
+      </c>
+      <c r="B233" s="14">
+        <v>12</v>
+      </c>
+      <c r="C233" s="10">
+        <v>4</v>
+      </c>
+      <c r="D233" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E233">
+        <f t="shared" si="10"/>
+        <v>19.2</v>
+      </c>
+      <c r="F233">
+        <f t="shared" si="11"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" s="8">
+        <v>35</v>
+      </c>
+      <c r="B234" s="14">
+        <v>12</v>
+      </c>
+      <c r="C234" s="10">
+        <v>4</v>
+      </c>
+      <c r="D234" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E234">
+        <f t="shared" si="10"/>
+        <v>19.2</v>
+      </c>
+      <c r="F234">
+        <f t="shared" si="11"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="8">
+        <v>35</v>
+      </c>
+      <c r="B235" s="14">
+        <v>12</v>
+      </c>
+      <c r="C235" s="10">
+        <v>5</v>
+      </c>
+      <c r="D235" s="2">
+        <v>0</v>
+      </c>
+      <c r="E235">
+        <f t="shared" si="10"/>
+        <v>24</v>
+      </c>
+      <c r="F235">
+        <f t="shared" si="11"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" s="8">
+        <v>35</v>
+      </c>
+      <c r="B236" s="14">
+        <v>12</v>
+      </c>
+      <c r="C236" s="10">
+        <v>5</v>
+      </c>
+      <c r="D236" s="4">
+        <v>4.45</v>
+      </c>
+      <c r="E236">
+        <f t="shared" si="10"/>
+        <v>24</v>
+      </c>
+      <c r="F236">
+        <f t="shared" si="11"/>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" s="8">
+        <v>35</v>
+      </c>
+      <c r="B237" s="14">
+        <v>12</v>
+      </c>
+      <c r="C237" s="10">
+        <v>5</v>
+      </c>
+      <c r="D237" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="E237">
+        <f t="shared" si="10"/>
+        <v>24</v>
+      </c>
+      <c r="F237">
+        <f t="shared" si="11"/>
+        <v>14.4</v>
       </c>
     </row>
   </sheetData>
